--- a/data/deregulated_utility_batteries.xlsx
+++ b/data/deregulated_utility_batteries.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dirkl\OneDrive\Desktop\ongoing_projects\MVS\dev\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78BA1E09-27BB-4DFA-B682-88E93F5BA0F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C232CD8-0EFA-46BC-A5C3-942AE6DB3C57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="groupby_state" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AB$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">groupby_state!$A$1:$C$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AB$59</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="211">
   <si>
     <t>Entity ID</t>
   </si>
@@ -657,13 +659,29 @@
   </si>
   <si>
     <t>Peak shaving?</t>
+  </si>
+  <si>
+    <t>Ancillary and arbitrage</t>
+  </si>
+  <si>
+    <t>GA</t>
+  </si>
+  <si>
+    <t>OR</t>
+  </si>
+  <si>
+    <t>Allowed market participation?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="169" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -680,6 +698,13 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -730,25 +755,28 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Comma" xfId="2" builtinId="3"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -3216,7 +3244,7 @@
         <v>-70.97645</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>17609</v>
       </c>
@@ -3281,7 +3309,7 @@
         <v>-117.9153</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>14328</v>
       </c>
@@ -3346,7 +3374,7 @@
         <v>-121.7818</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>11806</v>
       </c>
@@ -3411,7 +3439,7 @@
         <v>-71.047809999999998</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>16604</v>
       </c>
@@ -3476,7 +3504,7 @@
         <v>-98.617649999999998</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>4226</v>
       </c>
@@ -3541,7 +3569,7 @@
         <v>-73.840190000000007</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>56404</v>
       </c>
@@ -3605,8 +3633,14 @@
       <c r="U38">
         <v>-76.104029999999995</v>
       </c>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="W38" t="s">
+        <v>194</v>
+      </c>
+      <c r="X38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>15296</v>
       </c>
@@ -3671,7 +3705,7 @@
         <v>-74.118279999999999</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>17609</v>
       </c>
@@ -3736,7 +3770,7 @@
         <v>-118.0684</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>17609</v>
       </c>
@@ -3801,7 +3835,7 @@
         <v>-118.0684</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>14154</v>
       </c>
@@ -3865,8 +3899,21 @@
       <c r="U42">
         <v>-74.074669999999998</v>
       </c>
-    </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V42">
+        <v>7.4</v>
+      </c>
+      <c r="W42" t="s">
+        <v>194</v>
+      </c>
+      <c r="X42" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y42">
+        <f>23121 + 71114</f>
+        <v>94235</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>16609</v>
       </c>
@@ -3931,7 +3978,7 @@
         <v>-117.1344</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>16609</v>
       </c>
@@ -3996,7 +4043,7 @@
         <v>-117.1323</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>60868</v>
       </c>
@@ -4061,7 +4108,7 @@
         <v>-124.1044</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>4254</v>
       </c>
@@ -4126,7 +4173,7 @@
         <v>-85.724000000000004</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>4226</v>
       </c>
@@ -4191,7 +4238,7 @@
         <v>-74.077169999999995</v>
       </c>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>5248</v>
       </c>
@@ -4980,10 +5027,172 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AB1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:AB59" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <hyperlinks>
     <hyperlink ref="Z3" r:id="rId1" xr:uid="{2786AB65-18DC-4A3C-B0F2-1F923C184ACB}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFE5824D-1C0B-4DD4-9C7A-45E5A3C39C6B}">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="6">
+        <v>805.5</v>
+      </c>
+      <c r="C2" s="6">
+        <v>2635.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B3" s="6">
+        <v>92</v>
+      </c>
+      <c r="C3" s="6">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B4" s="6">
+        <v>65.2</v>
+      </c>
+      <c r="C4" s="6">
+        <v>260.39999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="6">
+        <v>60</v>
+      </c>
+      <c r="C5" s="6">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B6" s="6">
+        <v>34.5</v>
+      </c>
+      <c r="C6" s="6">
+        <v>78.2</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="6">
+        <v>19</v>
+      </c>
+      <c r="C7" s="6">
+        <v>68.099999999999994</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>95</v>
+      </c>
+      <c r="B8" s="6">
+        <v>11.5</v>
+      </c>
+      <c r="C8" s="6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="6">
+        <v>4</v>
+      </c>
+      <c r="C9" s="6">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B10" s="6">
+        <v>2.6</v>
+      </c>
+      <c r="C10" s="6">
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>101</v>
+      </c>
+      <c r="B11" s="6">
+        <v>1.4</v>
+      </c>
+      <c r="C11" s="6">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>107</v>
+      </c>
+      <c r="B12" s="6">
+        <v>0.3</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C1" xr:uid="{AFE5824D-1C0B-4DD4-9C7A-45E5A3C39C6B}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C12">
+      <sortCondition descending="1" ref="B1"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>